--- a/artfynd/A 63255-2023 artfynd.xlsx
+++ b/artfynd/A 63255-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63255-2023 artfynd.xlsx
+++ b/artfynd/A 63255-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>73882674</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717890.1635570629</v>
+        <v>717890</v>
       </c>
       <c r="R2" t="n">
-        <v>7061619.987096014</v>
+        <v>7061620</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73882681</v>
+        <v>103827359</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ledusjöheden, Ång</t>
+          <t>Ledusjöheden, Sunnansjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717890.1635570629</v>
+        <v>717877</v>
       </c>
       <c r="R3" t="n">
-        <v>7061619.987096014</v>
+        <v>7061463</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,33 +862,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>J-M Roberge, Anne-Maarit Hekkala</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100496886</v>
+        <v>103827371</v>
       </c>
       <c r="B4" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,46 +897,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ledusjöheden, Nordmaling, Ång</t>
+          <t>Ledusjöheden, Sunnansjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717937.3243683086</v>
+        <v>717919</v>
       </c>
       <c r="R4" t="n">
-        <v>7061622.789888026</v>
+        <v>7061469</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,37 +976,38 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>J-M Roberge</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Åsa Stenman</t>
+          <t>J-M Roberge, Anne-Maarit Hekkala</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103827654</v>
+        <v>103827511</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1071,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717873.5972729127</v>
+        <v>717906</v>
       </c>
       <c r="R5" t="n">
-        <v>7061575.123931524</v>
+        <v>7061525</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,19 +1079,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,19 +1114,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103827511</v>
+        <v>103827654</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1200,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717905.2490121629</v>
+        <v>717874</v>
       </c>
       <c r="R6" t="n">
-        <v>7061524.21222034</v>
+        <v>7061575</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,19 +1193,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,12 +1231,7 @@
         <v>103827643</v>
       </c>
       <c r="B7" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717894.0293856268</v>
+        <v>717894</v>
       </c>
       <c r="R7" t="n">
-        <v>7061544.408555896</v>
+        <v>7061544</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,19 +1307,9 @@
           <t>2022-09-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,6 +1359,209 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73882681</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>717890</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7061620</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100496886</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ledusjöheden, Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>717937</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7061623</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63255-2023 artfynd.xlsx
+++ b/artfynd/A 63255-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103827359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103827371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103827511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103827654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103827643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882681</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,8 +1602,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100496886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>